--- a/config/rules/CRS610MI.xlsx
+++ b/config/rules/CRS610MI.xlsx
@@ -3,14 +3,14 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Rules" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="_Audit_Log" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -27,6 +27,7 @@
     </font>
     <font>
       <name val="Calibri"/>
+      <family val="2"/>
       <b val="1"/>
       <sz val="11"/>
     </font>
@@ -519,13 +520,11 @@
           <t>ATPR</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>TODO</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -549,7 +548,6 @@
       <c r="J2" t="n">
         <v>1</v>
       </c>
-      <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -572,7 +570,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -596,7 +593,6 @@
       <c r="J3" t="n">
         <v>3</v>
       </c>
-      <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -609,13 +605,11 @@
           <t>STMS</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>TODO</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -668,7 +662,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -692,7 +685,6 @@
       <c r="J5" t="n">
         <v>12</v>
       </c>
-      <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -768,7 +760,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -792,7 +783,6 @@
       <c r="J7" t="n">
         <v>4</v>
       </c>
-      <c r="K7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -815,7 +805,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -839,7 +828,6 @@
       <c r="J8" t="n">
         <v>8</v>
       </c>
-      <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -862,7 +850,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -901,7 +888,6 @@
           <t>ADCA</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
           <t>CONST</t>
@@ -935,7 +921,6 @@
       <c r="J10" t="n">
         <v>3</v>
       </c>
-      <c r="K10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -958,7 +943,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -969,10 +953,6 @@
           <t>Mapped from TEDL</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -995,7 +975,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -1019,7 +998,6 @@
       <c r="J12" t="n">
         <v>6</v>
       </c>
-      <c r="K12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1042,7 +1020,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -1053,10 +1030,6 @@
           <t>Mapped from ADRT</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1079,7 +1052,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -1103,7 +1075,6 @@
       <c r="J14" t="n">
         <v>6</v>
       </c>
-      <c r="K14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1126,7 +1097,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -1150,7 +1120,6 @@
       <c r="J15" t="n">
         <v>12</v>
       </c>
-      <c r="K15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1173,7 +1142,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -1222,7 +1190,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -1246,7 +1213,6 @@
       <c r="J17" t="n">
         <v>16</v>
       </c>
-      <c r="K17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1269,7 +1235,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -1318,7 +1283,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -1367,7 +1331,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -1391,7 +1354,6 @@
       <c r="J20" t="n">
         <v>5</v>
       </c>
-      <c r="K20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1414,7 +1376,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -1463,7 +1424,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -1512,7 +1472,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -1536,7 +1495,6 @@
       <c r="J23" t="n">
         <v>12</v>
       </c>
-      <c r="K23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1559,7 +1517,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -1583,7 +1540,6 @@
       <c r="J24" t="n">
         <v>18</v>
       </c>
-      <c r="K24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1606,7 +1562,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -1655,7 +1610,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -1704,7 +1658,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -1753,7 +1706,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -1777,7 +1729,6 @@
       <c r="J28" t="n">
         <v>10</v>
       </c>
-      <c r="K28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1800,7 +1751,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -1849,7 +1799,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -1898,7 +1847,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -1922,7 +1870,6 @@
       <c r="J31" t="n">
         <v>2</v>
       </c>
-      <c r="K31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1945,7 +1892,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -1994,7 +1940,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -2043,7 +1988,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -2082,7 +2026,6 @@
           <t>BLPR</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
           <t>CONST</t>
@@ -2141,7 +2084,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -2165,7 +2107,6 @@
       <c r="J36" t="n">
         <v>1</v>
       </c>
-      <c r="K36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2188,7 +2129,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -2237,7 +2177,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -2286,7 +2225,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -2335,7 +2273,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -2346,10 +2283,6 @@
           <t>Mapped from LVDT</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2372,7 +2305,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -2396,7 +2328,6 @@
       <c r="J41" t="n">
         <v>3</v>
       </c>
-      <c r="K41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2419,7 +2350,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -2443,7 +2373,6 @@
       <c r="J42" t="n">
         <v>10</v>
       </c>
-      <c r="K42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2466,7 +2395,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -2490,7 +2418,6 @@
       <c r="J43" t="n">
         <v>10</v>
       </c>
-      <c r="K43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2513,7 +2440,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -2562,7 +2488,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -2586,7 +2511,6 @@
       <c r="J45" t="n">
         <v>11</v>
       </c>
-      <c r="K45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2609,7 +2533,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -2633,7 +2556,6 @@
       <c r="J46" t="n">
         <v>11</v>
       </c>
-      <c r="K46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2656,7 +2578,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -2705,7 +2626,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -2754,7 +2674,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -2803,7 +2722,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -2880,7 +2798,6 @@
       <c r="J51" t="n">
         <v>3</v>
       </c>
-      <c r="K51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2903,7 +2820,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -2927,7 +2843,6 @@
       <c r="J52" t="n">
         <v>36</v>
       </c>
-      <c r="K52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2950,7 +2865,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -2974,7 +2888,6 @@
       <c r="J53" t="n">
         <v>36</v>
       </c>
-      <c r="K53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2987,13 +2900,11 @@
           <t>CUA3</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
           <t>IGNORE</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -3017,7 +2928,6 @@
       <c r="J54" t="n">
         <v>36</v>
       </c>
-      <c r="K54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3030,13 +2940,11 @@
           <t>CUA4</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
           <t>IGNORE</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -3060,7 +2968,6 @@
       <c r="J55" t="n">
         <v>36</v>
       </c>
-      <c r="K55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3083,7 +2990,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -3107,7 +3013,6 @@
       <c r="J56" t="n">
         <v>3</v>
       </c>
-      <c r="K56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3130,7 +3035,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -3154,7 +3058,6 @@
       <c r="J57" t="n">
         <v>3</v>
       </c>
-      <c r="K57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3205,7 +3108,6 @@
       <c r="J58" t="n">
         <v>10</v>
       </c>
-      <c r="K58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3228,7 +3130,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -3252,7 +3153,6 @@
       <c r="J59" t="n">
         <v>36</v>
       </c>
-      <c r="K59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3275,7 +3175,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -3299,7 +3198,6 @@
       <c r="J60" t="n">
         <v>10</v>
       </c>
-      <c r="K60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3322,7 +3220,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -3346,7 +3243,6 @@
       <c r="J61" t="n">
         <v>10</v>
       </c>
-      <c r="K61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3369,7 +3265,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -3393,7 +3288,6 @@
       <c r="J62" t="n">
         <v>10</v>
       </c>
-      <c r="K62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3416,7 +3310,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -3495,7 +3388,6 @@
       <c r="J64" t="n">
         <v>2</v>
       </c>
-      <c r="K64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3518,7 +3410,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -3542,7 +3433,6 @@
       <c r="J65" t="n">
         <v>2</v>
       </c>
-      <c r="K65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3555,13 +3445,11 @@
           <t>DISY</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr">
         <is>
           <t>IGNORE</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -3585,7 +3473,6 @@
       <c r="J66" t="n">
         <v>10</v>
       </c>
-      <c r="K66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3608,7 +3495,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -3619,10 +3505,6 @@
           <t>Mapped from SPLM</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3645,7 +3527,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -3669,7 +3550,6 @@
       <c r="J68" t="n">
         <v>3</v>
       </c>
-      <c r="K68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3692,7 +3572,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -3741,7 +3620,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -3790,7 +3668,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -3869,7 +3746,6 @@
       <c r="J72" t="n">
         <v>2</v>
       </c>
-      <c r="K72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3892,7 +3768,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -3916,7 +3791,6 @@
       <c r="J73" t="n">
         <v>2</v>
       </c>
-      <c r="K73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3931,15 +3805,21 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>EDES</t>
+          <t>CSCD</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>DIRECT</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr"/>
+          <t>PYTHON</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>if str(source).strip().upper() not in ['US', 'CA']:
+    return row.get('CSCD', '')
+return row.get('ECAR', '')</t>
+        </is>
+      </c>
       <c r="F74" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -3963,7 +3843,6 @@
       <c r="J74" t="n">
         <v>10</v>
       </c>
-      <c r="K74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3986,7 +3865,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -4010,7 +3888,6 @@
       <c r="J75" t="n">
         <v>1</v>
       </c>
-      <c r="K75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4033,7 +3910,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -4057,7 +3933,6 @@
       <c r="J76" t="n">
         <v>3</v>
       </c>
-      <c r="K76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -4080,7 +3955,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -4091,10 +3965,6 @@
           <t>Mapped from MODL</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr"/>
-      <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -4117,7 +3987,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -4141,7 +4010,6 @@
       <c r="J78" t="n">
         <v>5</v>
       </c>
-      <c r="K78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -4164,7 +4032,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -4175,10 +4042,6 @@
           <t>Mapped from BCKO</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr"/>
-      <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -4201,7 +4064,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -4250,7 +4112,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -4299,7 +4160,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -4323,7 +4183,6 @@
       <c r="J82" t="n">
         <v>3</v>
       </c>
-      <c r="K82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -4346,7 +4205,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -4370,7 +4228,6 @@
       <c r="J83" t="n">
         <v>10</v>
       </c>
-      <c r="K83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -4393,7 +4250,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -4442,7 +4298,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -4491,7 +4346,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -4515,7 +4369,6 @@
       <c r="J86" t="n">
         <v>10</v>
       </c>
-      <c r="K86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -4538,7 +4391,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -4562,7 +4414,6 @@
       <c r="J87" t="n">
         <v>20</v>
       </c>
-      <c r="K87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -4585,7 +4436,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -4664,7 +4514,6 @@
       <c r="J89" t="n">
         <v>2</v>
       </c>
-      <c r="K89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -4687,7 +4536,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -4698,10 +4546,6 @@
           <t>Mapped from PADL</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr"/>
-      <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -4724,7 +4568,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -4748,7 +4591,6 @@
       <c r="J91" t="n">
         <v>10</v>
       </c>
-      <c r="K91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -4761,7 +4603,6 @@
           <t>MODL</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr">
         <is>
           <t>CONST</t>
@@ -4795,7 +4636,6 @@
       <c r="J92" t="n">
         <v>3</v>
       </c>
-      <c r="K92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -4818,7 +4658,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -4867,7 +4706,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -4916,7 +4754,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -4965,7 +4802,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -5014,7 +4850,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -5038,7 +4873,6 @@
       <c r="J97" t="n">
         <v>30</v>
       </c>
-      <c r="K97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -5089,7 +4923,6 @@
       <c r="J98" t="n">
         <v>3</v>
       </c>
-      <c r="K98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -5112,7 +4945,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -5161,7 +4993,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -5210,7 +5041,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -5234,7 +5064,6 @@
       <c r="J101" t="n">
         <v>16</v>
       </c>
-      <c r="K101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -5257,7 +5086,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -5281,7 +5109,6 @@
       <c r="J102" t="n">
         <v>16</v>
       </c>
-      <c r="K102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -5304,7 +5131,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -5315,10 +5141,6 @@
           <t>Mapped from BOP1</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr"/>
-      <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
-      <c r="K103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -5341,7 +5163,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -5365,7 +5186,6 @@
       <c r="J104" t="n">
         <v>10</v>
       </c>
-      <c r="K104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -5388,7 +5208,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -5412,7 +5231,6 @@
       <c r="J105" t="n">
         <v>30</v>
       </c>
-      <c r="K105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -5435,7 +5253,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -5484,7 +5301,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -5533,7 +5349,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -5557,7 +5372,6 @@
       <c r="J108" t="n">
         <v>2</v>
       </c>
-      <c r="K108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -5580,7 +5394,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -5604,7 +5417,6 @@
       <c r="J109" t="n">
         <v>10</v>
       </c>
-      <c r="K109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -5655,7 +5467,6 @@
       <c r="J110" t="n">
         <v>3</v>
       </c>
-      <c r="K110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -5678,7 +5489,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -5702,7 +5512,6 @@
       <c r="J111" t="n">
         <v>3</v>
       </c>
-      <c r="K111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -5725,7 +5534,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -5749,7 +5557,6 @@
       <c r="J112" t="n">
         <v>10</v>
       </c>
-      <c r="K112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -5772,7 +5579,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -5821,7 +5627,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -5845,7 +5650,6 @@
       <c r="J114" t="n">
         <v>10</v>
       </c>
-      <c r="K114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -5858,15 +5662,14 @@
           <t>RESP</t>
         </is>
       </c>
-      <c r="C115" t="inlineStr"/>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>RESP</t>
+        </is>
+      </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>CONST</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>W40</t>
+          <t>DIRECT</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -5892,7 +5695,6 @@
       <c r="J115" t="n">
         <v>10</v>
       </c>
-      <c r="K115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -5905,7 +5707,6 @@
           <t>RMCT</t>
         </is>
       </c>
-      <c r="C116" t="inlineStr"/>
       <c r="D116" t="inlineStr">
         <is>
           <t>CONST</t>
@@ -5939,7 +5740,6 @@
       <c r="J116" t="n">
         <v>3</v>
       </c>
-      <c r="K116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -5962,7 +5762,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -5973,10 +5772,6 @@
           <t>Mapped from CSCD</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr"/>
-      <c r="I117" t="inlineStr"/>
-      <c r="J117" t="inlineStr"/>
-      <c r="K117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -5999,7 +5794,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -6048,7 +5842,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -6072,7 +5865,6 @@
       <c r="J119" t="n">
         <v>10</v>
       </c>
-      <c r="K119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -6095,7 +5887,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -6119,7 +5910,6 @@
       <c r="J120" t="n">
         <v>10</v>
       </c>
-      <c r="K120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -6142,7 +5932,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -6166,7 +5955,6 @@
       <c r="J121" t="n">
         <v>8</v>
       </c>
-      <c r="K121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -6189,7 +5977,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -6213,7 +6000,6 @@
       <c r="J122" t="n">
         <v>2</v>
       </c>
-      <c r="K122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -6226,7 +6012,6 @@
           <t>STMR</t>
         </is>
       </c>
-      <c r="C123" t="inlineStr"/>
       <c r="D123" t="inlineStr">
         <is>
           <t>CONST</t>
@@ -6260,7 +6045,6 @@
       <c r="J123" t="n">
         <v>3</v>
       </c>
-      <c r="K123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -6283,7 +6067,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -6307,7 +6090,6 @@
       <c r="J124" t="n">
         <v>3</v>
       </c>
-      <c r="K124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -6330,7 +6112,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -6379,7 +6160,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -6428,7 +6208,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -6452,7 +6231,6 @@
       <c r="J127" t="n">
         <v>3</v>
       </c>
-      <c r="K127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -6475,7 +6253,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -6499,7 +6276,6 @@
       <c r="J128" t="n">
         <v>20</v>
       </c>
-      <c r="K128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -6550,7 +6326,6 @@
       <c r="J129" t="n">
         <v>3</v>
       </c>
-      <c r="K129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -6573,7 +6348,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -6622,7 +6396,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -6633,10 +6406,6 @@
           <t>Mapped from TAXC</t>
         </is>
       </c>
-      <c r="H131" t="inlineStr"/>
-      <c r="I131" t="inlineStr"/>
-      <c r="J131" t="inlineStr"/>
-      <c r="K131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -6659,7 +6428,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -6683,7 +6451,6 @@
       <c r="J132" t="n">
         <v>3</v>
       </c>
-      <c r="K132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -6706,7 +6473,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -6730,7 +6496,6 @@
       <c r="J133" t="n">
         <v>3</v>
       </c>
-      <c r="K133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -6753,7 +6518,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -6777,7 +6541,6 @@
       <c r="J134" t="n">
         <v>16</v>
       </c>
-      <c r="K134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -6800,7 +6563,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -6849,7 +6611,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -6873,7 +6634,6 @@
       <c r="J136" t="n">
         <v>20</v>
       </c>
-      <c r="K136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -6896,7 +6656,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -6920,7 +6679,6 @@
       <c r="J137" t="n">
         <v>5</v>
       </c>
-      <c r="K137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -6943,7 +6701,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -6967,7 +6724,6 @@
       <c r="J138" t="n">
         <v>10</v>
       </c>
-      <c r="K138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -6990,7 +6746,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -7014,7 +6769,6 @@
       <c r="J139" t="n">
         <v>10</v>
       </c>
-      <c r="K139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -7037,7 +6791,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -7061,7 +6814,6 @@
       <c r="J140" t="n">
         <v>16</v>
       </c>
-      <c r="K140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -7084,7 +6836,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -7133,7 +6884,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -7157,7 +6907,6 @@
       <c r="J142" t="n">
         <v>3</v>
       </c>
-      <c r="K142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -7180,7 +6929,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -7204,7 +6952,6 @@
       <c r="J143" t="n">
         <v>30</v>
       </c>
-      <c r="K143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -7217,13 +6964,11 @@
           <t>ACEI</t>
         </is>
       </c>
-      <c r="C144" t="inlineStr"/>
       <c r="D144" t="inlineStr">
         <is>
           <t>IGNORE</t>
         </is>
       </c>
-      <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -7262,13 +7007,11 @@
           <t>ACGR</t>
         </is>
       </c>
-      <c r="C145" t="inlineStr"/>
       <c r="D145" t="inlineStr">
         <is>
           <t>IGNORE</t>
         </is>
       </c>
-      <c r="E145" t="inlineStr"/>
       <c r="F145" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -7292,7 +7035,6 @@
       <c r="J145" t="n">
         <v>10</v>
       </c>
-      <c r="K145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -7305,13 +7047,11 @@
           <t>AOTP</t>
         </is>
       </c>
-      <c r="C146" t="inlineStr"/>
       <c r="D146" t="inlineStr">
         <is>
           <t>IGNORE</t>
         </is>
       </c>
-      <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -7335,7 +7075,6 @@
       <c r="J146" t="n">
         <v>3</v>
       </c>
-      <c r="K146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -7348,13 +7087,11 @@
           <t>CCUS</t>
         </is>
       </c>
-      <c r="C147" t="inlineStr"/>
       <c r="D147" t="inlineStr">
         <is>
           <t>IGNORE</t>
         </is>
       </c>
-      <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -7378,7 +7115,6 @@
       <c r="J147" t="n">
         <v>10</v>
       </c>
-      <c r="K147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -7391,13 +7127,11 @@
           <t>CFC0</t>
         </is>
       </c>
-      <c r="C148" t="inlineStr"/>
       <c r="D148" t="inlineStr">
         <is>
           <t>IGNORE</t>
         </is>
       </c>
-      <c r="E148" t="inlineStr"/>
       <c r="F148" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -7421,7 +7155,6 @@
       <c r="J148" t="n">
         <v>1</v>
       </c>
-      <c r="K148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -7434,13 +7167,11 @@
           <t>CFC1</t>
         </is>
       </c>
-      <c r="C149" t="inlineStr"/>
       <c r="D149" t="inlineStr">
         <is>
           <t>IGNORE</t>
         </is>
       </c>
-      <c r="E149" t="inlineStr"/>
       <c r="F149" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -7464,7 +7195,6 @@
       <c r="J149" t="n">
         <v>10</v>
       </c>
-      <c r="K149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -7477,13 +7207,11 @@
           <t>CFC2</t>
         </is>
       </c>
-      <c r="C150" t="inlineStr"/>
       <c r="D150" t="inlineStr">
         <is>
           <t>IGNORE</t>
         </is>
       </c>
-      <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -7522,13 +7250,11 @@
           <t>CFC3</t>
         </is>
       </c>
-      <c r="C151" t="inlineStr"/>
       <c r="D151" t="inlineStr">
         <is>
           <t>IGNORE</t>
         </is>
       </c>
-      <c r="E151" t="inlineStr"/>
       <c r="F151" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -7552,7 +7278,6 @@
       <c r="J151" t="n">
         <v>3</v>
       </c>
-      <c r="K151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -7565,13 +7290,11 @@
           <t>CFC4</t>
         </is>
       </c>
-      <c r="C152" t="inlineStr"/>
       <c r="D152" t="inlineStr">
         <is>
           <t>IGNORE</t>
         </is>
       </c>
-      <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -7595,7 +7318,6 @@
       <c r="J152" t="n">
         <v>5</v>
       </c>
-      <c r="K152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -7608,13 +7330,11 @@
           <t>CFC5</t>
         </is>
       </c>
-      <c r="C153" t="inlineStr"/>
       <c r="D153" t="inlineStr">
         <is>
           <t>IGNORE</t>
         </is>
       </c>
-      <c r="E153" t="inlineStr"/>
       <c r="F153" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -7638,7 +7358,6 @@
       <c r="J153" t="n">
         <v>1</v>
       </c>
-      <c r="K153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -7651,13 +7370,11 @@
           <t>CFC7</t>
         </is>
       </c>
-      <c r="C154" t="inlineStr"/>
       <c r="D154" t="inlineStr">
         <is>
           <t>IGNORE</t>
         </is>
       </c>
-      <c r="E154" t="inlineStr"/>
       <c r="F154" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -7696,13 +7413,11 @@
           <t>CFC8</t>
         </is>
       </c>
-      <c r="C155" t="inlineStr"/>
       <c r="D155" t="inlineStr">
         <is>
           <t>IGNORE</t>
         </is>
       </c>
-      <c r="E155" t="inlineStr"/>
       <c r="F155" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -7726,7 +7441,6 @@
       <c r="J155" t="n">
         <v>3</v>
       </c>
-      <c r="K155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -7739,13 +7453,11 @@
           <t>CFC9</t>
         </is>
       </c>
-      <c r="C156" t="inlineStr"/>
       <c r="D156" t="inlineStr">
         <is>
           <t>IGNORE</t>
         </is>
       </c>
-      <c r="E156" t="inlineStr"/>
       <c r="F156" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -7769,7 +7481,6 @@
       <c r="J156" t="n">
         <v>5</v>
       </c>
-      <c r="K156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -7782,13 +7493,11 @@
           <t>CNTN</t>
         </is>
       </c>
-      <c r="C157" t="inlineStr"/>
       <c r="D157" t="inlineStr">
         <is>
           <t>IGNORE</t>
         </is>
       </c>
-      <c r="E157" t="inlineStr"/>
       <c r="F157" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -7812,7 +7521,6 @@
       <c r="J157" t="n">
         <v>40</v>
       </c>
-      <c r="K157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -7825,13 +7533,11 @@
           <t>DOGR</t>
         </is>
       </c>
-      <c r="C158" t="inlineStr"/>
       <c r="D158" t="inlineStr">
         <is>
           <t>IGNORE</t>
         </is>
       </c>
-      <c r="E158" t="inlineStr"/>
       <c r="F158" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -7855,7 +7561,6 @@
       <c r="J158" t="n">
         <v>3</v>
       </c>
-      <c r="K158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -7868,13 +7573,11 @@
           <t>DPOT</t>
         </is>
       </c>
-      <c r="C159" t="inlineStr"/>
       <c r="D159" t="inlineStr">
         <is>
           <t>IGNORE</t>
         </is>
       </c>
-      <c r="E159" t="inlineStr"/>
       <c r="F159" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -7913,13 +7616,11 @@
           <t>DTE1</t>
         </is>
       </c>
-      <c r="C160" t="inlineStr"/>
       <c r="D160" t="inlineStr">
         <is>
           <t>IGNORE</t>
         </is>
       </c>
-      <c r="E160" t="inlineStr"/>
       <c r="F160" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -7958,13 +7659,11 @@
           <t>DTE2</t>
         </is>
       </c>
-      <c r="C161" t="inlineStr"/>
       <c r="D161" t="inlineStr">
         <is>
           <t>IGNORE</t>
         </is>
       </c>
-      <c r="E161" t="inlineStr"/>
       <c r="F161" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -8003,13 +7702,11 @@
           <t>DTE3</t>
         </is>
       </c>
-      <c r="C162" t="inlineStr"/>
       <c r="D162" t="inlineStr">
         <is>
           <t>IGNORE</t>
         </is>
       </c>
-      <c r="E162" t="inlineStr"/>
       <c r="F162" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -8048,13 +7745,11 @@
           <t>DTL1</t>
         </is>
       </c>
-      <c r="C163" t="inlineStr"/>
       <c r="D163" t="inlineStr">
         <is>
           <t>IGNORE</t>
         </is>
       </c>
-      <c r="E163" t="inlineStr"/>
       <c r="F163" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -8065,7 +7760,6 @@
           <t>MCO listed but not required</t>
         </is>
       </c>
-      <c r="H163" t="inlineStr"/>
       <c r="I163" t="inlineStr">
         <is>
           <t>Decimal</t>
@@ -8089,13 +7783,11 @@
           <t>EXCD</t>
         </is>
       </c>
-      <c r="C164" t="inlineStr"/>
       <c r="D164" t="inlineStr">
         <is>
           <t>IGNORE</t>
         </is>
       </c>
-      <c r="E164" t="inlineStr"/>
       <c r="F164" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -8119,7 +7811,6 @@
       <c r="J164" t="n">
         <v>2</v>
       </c>
-      <c r="K164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -8132,13 +7823,11 @@
           <t>EXPR</t>
         </is>
       </c>
-      <c r="C165" t="inlineStr"/>
       <c r="D165" t="inlineStr">
         <is>
           <t>IGNORE</t>
         </is>
       </c>
-      <c r="E165" t="inlineStr"/>
       <c r="F165" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -8177,13 +7866,11 @@
           <t>FRE2</t>
         </is>
       </c>
-      <c r="C166" t="inlineStr"/>
       <c r="D166" t="inlineStr">
         <is>
           <t>IGNORE</t>
         </is>
       </c>
-      <c r="E166" t="inlineStr"/>
       <c r="F166" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -8207,7 +7894,6 @@
       <c r="J166" t="n">
         <v>5</v>
       </c>
-      <c r="K166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -8220,13 +7906,11 @@
           <t>GEOX</t>
         </is>
       </c>
-      <c r="C167" t="inlineStr"/>
       <c r="D167" t="inlineStr">
         <is>
           <t>IGNORE</t>
         </is>
       </c>
-      <c r="E167" t="inlineStr"/>
       <c r="F167" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -8237,10 +7921,6 @@
           <t>MCO listed but not required</t>
         </is>
       </c>
-      <c r="H167" t="inlineStr"/>
-      <c r="I167" t="inlineStr"/>
-      <c r="J167" t="inlineStr"/>
-      <c r="K167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -8253,13 +7933,11 @@
           <t>GEOY</t>
         </is>
       </c>
-      <c r="C168" t="inlineStr"/>
       <c r="D168" t="inlineStr">
         <is>
           <t>IGNORE</t>
         </is>
       </c>
-      <c r="E168" t="inlineStr"/>
       <c r="F168" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -8270,10 +7948,6 @@
           <t>MCO listed but not required</t>
         </is>
       </c>
-      <c r="H168" t="inlineStr"/>
-      <c r="I168" t="inlineStr"/>
-      <c r="J168" t="inlineStr"/>
-      <c r="K168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -8286,13 +7960,11 @@
           <t>GEOZ</t>
         </is>
       </c>
-      <c r="C169" t="inlineStr"/>
       <c r="D169" t="inlineStr">
         <is>
           <t>IGNORE</t>
         </is>
       </c>
-      <c r="E169" t="inlineStr"/>
       <c r="F169" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -8303,10 +7975,6 @@
           <t>MCO listed but not required</t>
         </is>
       </c>
-      <c r="H169" t="inlineStr"/>
-      <c r="I169" t="inlineStr"/>
-      <c r="J169" t="inlineStr"/>
-      <c r="K169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -8319,13 +7987,11 @@
           <t>IIDA</t>
         </is>
       </c>
-      <c r="C170" t="inlineStr"/>
       <c r="D170" t="inlineStr">
         <is>
           <t>IGNORE</t>
         </is>
       </c>
-      <c r="E170" t="inlineStr"/>
       <c r="F170" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -8364,13 +8030,11 @@
           <t>IIMO</t>
         </is>
       </c>
-      <c r="C171" t="inlineStr"/>
       <c r="D171" t="inlineStr">
         <is>
           <t>IGNORE</t>
         </is>
       </c>
-      <c r="E171" t="inlineStr"/>
       <c r="F171" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -8409,13 +8073,11 @@
           <t>IIYR</t>
         </is>
       </c>
-      <c r="C172" t="inlineStr"/>
       <c r="D172" t="inlineStr">
         <is>
           <t>IGNORE</t>
         </is>
       </c>
-      <c r="E172" t="inlineStr"/>
       <c r="F172" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -8454,13 +8116,11 @@
           <t>IVGP</t>
         </is>
       </c>
-      <c r="C173" t="inlineStr"/>
       <c r="D173" t="inlineStr">
         <is>
           <t>IGNORE</t>
         </is>
       </c>
-      <c r="E173" t="inlineStr"/>
       <c r="F173" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -8484,7 +8144,6 @@
       <c r="J173" t="n">
         <v>3</v>
       </c>
-      <c r="K173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -8497,13 +8156,11 @@
           <t>LSAD</t>
         </is>
       </c>
-      <c r="C174" t="inlineStr"/>
       <c r="D174" t="inlineStr">
         <is>
           <t>IGNORE</t>
         </is>
       </c>
-      <c r="E174" t="inlineStr"/>
       <c r="F174" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -8527,7 +8184,6 @@
       <c r="J174" t="n">
         <v>8</v>
       </c>
-      <c r="K174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -8540,13 +8196,11 @@
           <t>LSID</t>
         </is>
       </c>
-      <c r="C175" t="inlineStr"/>
       <c r="D175" t="inlineStr">
         <is>
           <t>IGNORE</t>
         </is>
       </c>
-      <c r="E175" t="inlineStr"/>
       <c r="F175" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -8570,7 +8224,6 @@
       <c r="J175" t="n">
         <v>8</v>
       </c>
-      <c r="K175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -8583,13 +8236,11 @@
           <t>MCOS</t>
         </is>
       </c>
-      <c r="C176" t="inlineStr"/>
       <c r="D176" t="inlineStr">
         <is>
           <t>IGNORE</t>
         </is>
       </c>
-      <c r="E176" t="inlineStr"/>
       <c r="F176" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -8628,13 +8279,11 @@
           <t>MIHP</t>
         </is>
       </c>
-      <c r="C177" t="inlineStr"/>
       <c r="D177" t="inlineStr">
         <is>
           <t>IGNORE</t>
         </is>
       </c>
-      <c r="E177" t="inlineStr"/>
       <c r="F177" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -8673,13 +8322,11 @@
           <t>MINV</t>
         </is>
       </c>
-      <c r="C178" t="inlineStr"/>
       <c r="D178" t="inlineStr">
         <is>
           <t>IGNORE</t>
         </is>
       </c>
-      <c r="E178" t="inlineStr"/>
       <c r="F178" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -8718,13 +8365,11 @@
           <t>MRTP</t>
         </is>
       </c>
-      <c r="C179" t="inlineStr"/>
       <c r="D179" t="inlineStr">
         <is>
           <t>IGNORE</t>
         </is>
       </c>
-      <c r="E179" t="inlineStr"/>
       <c r="F179" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -8763,13 +8408,11 @@
           <t>OPAY</t>
         </is>
       </c>
-      <c r="C180" t="inlineStr"/>
       <c r="D180" t="inlineStr">
         <is>
           <t>IGNORE</t>
         </is>
       </c>
-      <c r="E180" t="inlineStr"/>
       <c r="F180" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -8808,13 +8451,11 @@
           <t>OT75</t>
         </is>
       </c>
-      <c r="C181" t="inlineStr"/>
       <c r="D181" t="inlineStr">
         <is>
           <t>IGNORE</t>
         </is>
       </c>
-      <c r="E181" t="inlineStr"/>
       <c r="F181" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -8853,13 +8494,11 @@
           <t>PLTB</t>
         </is>
       </c>
-      <c r="C182" t="inlineStr"/>
       <c r="D182" t="inlineStr">
         <is>
           <t>IGNORE</t>
         </is>
       </c>
-      <c r="E182" t="inlineStr"/>
       <c r="F182" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -8883,7 +8522,6 @@
       <c r="J182" t="n">
         <v>10</v>
       </c>
-      <c r="K182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -8896,13 +8534,11 @@
           <t>PRDL</t>
         </is>
       </c>
-      <c r="C183" t="inlineStr"/>
       <c r="D183" t="inlineStr">
         <is>
           <t>IGNORE</t>
         </is>
       </c>
-      <c r="E183" t="inlineStr"/>
       <c r="F183" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -8941,13 +8577,11 @@
           <t>PYGR</t>
         </is>
       </c>
-      <c r="C184" t="inlineStr"/>
       <c r="D184" t="inlineStr">
         <is>
           <t>IGNORE</t>
         </is>
       </c>
-      <c r="E184" t="inlineStr"/>
       <c r="F184" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -8986,13 +8620,11 @@
           <t>QUCK</t>
         </is>
       </c>
-      <c r="C185" t="inlineStr"/>
       <c r="D185" t="inlineStr">
         <is>
           <t>IGNORE</t>
         </is>
       </c>
-      <c r="E185" t="inlineStr"/>
       <c r="F185" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -9031,13 +8663,11 @@
           <t>RAFA</t>
         </is>
       </c>
-      <c r="C186" t="inlineStr"/>
       <c r="D186" t="inlineStr">
         <is>
           <t>IGNORE</t>
         </is>
       </c>
-      <c r="E186" t="inlineStr"/>
       <c r="F186" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -9076,13 +8706,11 @@
           <t>RAN1</t>
         </is>
       </c>
-      <c r="C187" t="inlineStr"/>
       <c r="D187" t="inlineStr">
         <is>
           <t>IGNORE</t>
         </is>
       </c>
-      <c r="E187" t="inlineStr"/>
       <c r="F187" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -9121,13 +8749,11 @@
           <t>RAN2</t>
         </is>
       </c>
-      <c r="C188" t="inlineStr"/>
       <c r="D188" t="inlineStr">
         <is>
           <t>IGNORE</t>
         </is>
       </c>
-      <c r="E188" t="inlineStr"/>
       <c r="F188" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -9166,13 +8792,11 @@
           <t>RAN3</t>
         </is>
       </c>
-      <c r="C189" t="inlineStr"/>
       <c r="D189" t="inlineStr">
         <is>
           <t>IGNORE</t>
         </is>
       </c>
-      <c r="E189" t="inlineStr"/>
       <c r="F189" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -9211,13 +8835,11 @@
           <t>RAN4</t>
         </is>
       </c>
-      <c r="C190" t="inlineStr"/>
       <c r="D190" t="inlineStr">
         <is>
           <t>IGNORE</t>
         </is>
       </c>
-      <c r="E190" t="inlineStr"/>
       <c r="F190" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -9256,13 +8878,11 @@
           <t>RDIS</t>
         </is>
       </c>
-      <c r="C191" t="inlineStr"/>
       <c r="D191" t="inlineStr">
         <is>
           <t>IGNORE</t>
         </is>
       </c>
-      <c r="E191" t="inlineStr"/>
       <c r="F191" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -9286,7 +8906,6 @@
       <c r="J191" t="n">
         <v>10</v>
       </c>
-      <c r="K191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -9299,13 +8918,11 @@
           <t>RPLT</t>
         </is>
       </c>
-      <c r="C192" t="inlineStr"/>
       <c r="D192" t="inlineStr">
         <is>
           <t>IGNORE</t>
         </is>
       </c>
-      <c r="E192" t="inlineStr"/>
       <c r="F192" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -9329,7 +8946,6 @@
       <c r="J192" t="n">
         <v>10</v>
       </c>
-      <c r="K192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -9342,13 +8958,11 @@
           <t>RSMC</t>
         </is>
       </c>
-      <c r="C193" t="inlineStr"/>
       <c r="D193" t="inlineStr">
         <is>
           <t>IGNORE</t>
         </is>
       </c>
-      <c r="E193" t="inlineStr"/>
       <c r="F193" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -9372,7 +8986,6 @@
       <c r="J193" t="n">
         <v>10</v>
       </c>
-      <c r="K193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -9385,13 +8998,11 @@
           <t>RTEP</t>
         </is>
       </c>
-      <c r="C194" t="inlineStr"/>
       <c r="D194" t="inlineStr">
         <is>
           <t>IGNORE</t>
         </is>
       </c>
-      <c r="E194" t="inlineStr"/>
       <c r="F194" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -9415,7 +9026,6 @@
       <c r="J194" t="n">
         <v>3</v>
       </c>
-      <c r="K194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -9428,13 +9038,11 @@
           <t>RTMO</t>
         </is>
       </c>
-      <c r="C195" t="inlineStr"/>
       <c r="D195" t="inlineStr">
         <is>
           <t>IGNORE</t>
         </is>
       </c>
-      <c r="E195" t="inlineStr"/>
       <c r="F195" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -9473,13 +9081,11 @@
           <t>RTYR</t>
         </is>
       </c>
-      <c r="C196" t="inlineStr"/>
       <c r="D196" t="inlineStr">
         <is>
           <t>IGNORE</t>
         </is>
       </c>
-      <c r="E196" t="inlineStr"/>
       <c r="F196" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -9518,13 +9124,11 @@
           <t>SECD</t>
         </is>
       </c>
-      <c r="C197" t="inlineStr"/>
       <c r="D197" t="inlineStr">
         <is>
           <t>IGNORE</t>
         </is>
       </c>
-      <c r="E197" t="inlineStr"/>
       <c r="F197" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -9563,13 +9167,11 @@
           <t>ST75</t>
         </is>
       </c>
-      <c r="C198" t="inlineStr"/>
       <c r="D198" t="inlineStr">
         <is>
           <t>IGNORE</t>
         </is>
       </c>
-      <c r="E198" t="inlineStr"/>
       <c r="F198" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -9608,13 +9210,11 @@
           <t>ST76</t>
         </is>
       </c>
-      <c r="C199" t="inlineStr"/>
       <c r="D199" t="inlineStr">
         <is>
           <t>IGNORE</t>
         </is>
       </c>
-      <c r="E199" t="inlineStr"/>
       <c r="F199" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -9653,13 +9253,11 @@
           <t>ST77</t>
         </is>
       </c>
-      <c r="C200" t="inlineStr"/>
       <c r="D200" t="inlineStr">
         <is>
           <t>IGNORE</t>
         </is>
       </c>
-      <c r="E200" t="inlineStr"/>
       <c r="F200" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -9698,13 +9296,11 @@
           <t>ST78</t>
         </is>
       </c>
-      <c r="C201" t="inlineStr"/>
       <c r="D201" t="inlineStr">
         <is>
           <t>IGNORE</t>
         </is>
       </c>
-      <c r="E201" t="inlineStr"/>
       <c r="F201" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -9743,13 +9339,11 @@
           <t>TRSU</t>
         </is>
       </c>
-      <c r="C202" t="inlineStr"/>
       <c r="D202" t="inlineStr">
         <is>
           <t>IGNORE</t>
         </is>
       </c>
-      <c r="E202" t="inlineStr"/>
       <c r="F202" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -9773,7 +9367,6 @@
       <c r="J202" t="n">
         <v>10</v>
       </c>
-      <c r="K202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -9786,13 +9379,11 @@
           <t>TXAP</t>
         </is>
       </c>
-      <c r="C203" t="inlineStr"/>
       <c r="D203" t="inlineStr">
         <is>
           <t>IGNORE</t>
         </is>
       </c>
-      <c r="E203" t="inlineStr"/>
       <c r="F203" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -9831,13 +9422,11 @@
           <t>USR1</t>
         </is>
       </c>
-      <c r="C204" t="inlineStr"/>
       <c r="D204" t="inlineStr">
         <is>
           <t>IGNORE</t>
         </is>
       </c>
-      <c r="E204" t="inlineStr"/>
       <c r="F204" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -9861,7 +9450,6 @@
       <c r="J204" t="n">
         <v>10</v>
       </c>
-      <c r="K204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -9874,13 +9462,11 @@
           <t>USR2</t>
         </is>
       </c>
-      <c r="C205" t="inlineStr"/>
       <c r="D205" t="inlineStr">
         <is>
           <t>IGNORE</t>
         </is>
       </c>
-      <c r="E205" t="inlineStr"/>
       <c r="F205" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -9904,7 +9490,6 @@
       <c r="J205" t="n">
         <v>10</v>
       </c>
-      <c r="K205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -9917,13 +9502,11 @@
           <t>USR3</t>
         </is>
       </c>
-      <c r="C206" t="inlineStr"/>
       <c r="D206" t="inlineStr">
         <is>
           <t>IGNORE</t>
         </is>
       </c>
-      <c r="E206" t="inlineStr"/>
       <c r="F206" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -9947,7 +9530,6 @@
       <c r="J206" t="n">
         <v>10</v>
       </c>
-      <c r="K206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -9960,13 +9542,11 @@
           <t>VDLA</t>
         </is>
       </c>
-      <c r="C207" t="inlineStr"/>
       <c r="D207" t="inlineStr">
         <is>
           <t>IGNORE</t>
         </is>
       </c>
-      <c r="E207" t="inlineStr"/>
       <c r="F207" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -10005,13 +9585,11 @@
           <t>YRE2</t>
         </is>
       </c>
-      <c r="C208" t="inlineStr"/>
       <c r="D208" t="inlineStr">
         <is>
           <t>IGNORE</t>
         </is>
       </c>
-      <c r="E208" t="inlineStr"/>
       <c r="F208" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -10035,7 +9613,6 @@
       <c r="J208" t="n">
         <v>30</v>
       </c>
-      <c r="K208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -10086,7 +9663,6 @@
       <c r="J209" t="n">
         <v>10</v>
       </c>
-      <c r="K209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -10137,7 +9713,6 @@
       <c r="J210" t="n">
         <v>10</v>
       </c>
-      <c r="K210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -10188,7 +9763,6 @@
       <c r="J211" t="n">
         <v>10</v>
       </c>
-      <c r="K211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -10239,7 +9813,6 @@
       <c r="J212" t="n">
         <v>10</v>
       </c>
-      <c r="K212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -10290,7 +9863,6 @@
       <c r="J213" t="n">
         <v>10</v>
       </c>
-      <c r="K213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -10343,7 +9915,6 @@
       <c r="J214" t="n">
         <v>10</v>
       </c>
-      <c r="K214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -10356,13 +9927,11 @@
           <t>CONO</t>
         </is>
       </c>
-      <c r="C215" t="inlineStr"/>
       <c r="D215" t="inlineStr">
         <is>
           <t>IGNORE</t>
         </is>
       </c>
-      <c r="E215" t="inlineStr"/>
       <c r="F215" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -10411,7 +9980,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E216" t="inlineStr"/>
       <c r="F216" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -10435,7 +10003,6 @@
       <c r="J216" t="n">
         <v>2</v>
       </c>
-      <c r="K216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -10458,7 +10025,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E217" t="inlineStr"/>
       <c r="F217" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -10469,7 +10035,6 @@
           <t>Mapped from  TXVR</t>
         </is>
       </c>
-      <c r="H217" t="inlineStr"/>
       <c r="I217" t="inlineStr">
         <is>
           <t>String</t>
@@ -10478,7 +10043,6 @@
       <c r="J217" t="n">
         <v>10</v>
       </c>
-      <c r="K217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -10501,7 +10065,6 @@
           <t>DIRECT</t>
         </is>
       </c>
-      <c r="E218" t="inlineStr"/>
       <c r="F218" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -10525,7 +10088,6 @@
       <c r="J218" t="n">
         <v>60</v>
       </c>
-      <c r="K218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -10597,7 +10159,6 @@
       <c r="J219" t="n">
         <v>10</v>
       </c>
-      <c r="K219" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10610,7 +10171,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E38"/>
+  <dimension ref="A1:E42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
@@ -11705,6 +11266,116 @@
         </is>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-05-08 11:24:42</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>w10itasv</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>EDIT</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>EDES</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Src: EDES-&gt;ECAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-05-08 11:47:19</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>w10itasv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>EDIT</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>RESP</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Type: CONST-&gt;DIRECT, Val: 'W40'-&gt;''</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-05-08 12:24:29</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>w10itasv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>EDIT</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>EDES</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Type: DIRECT-&gt;PYTHON, Src: ECAR-&gt;CSCD, Val: ''-&gt;'if str(source).strip().upper() not in ['US', 'CA']:
+    return row.get('CSCD', '')
+return row.get('ECAR', '')'</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-05-08 12:24:29</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>w10itasv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>EDIT</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>RESP</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Src: -&gt;RESP</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/rules/CRS610MI.xlsx
+++ b/config/rules/CRS610MI.xlsx
@@ -6064,7 +6064,16 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>DIRECT</t>
+          <t>PYTHON</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>if str(source).strip() == '001':
+    return 'TAX'
+elif str(source).strip() == '000':
+    return 'NOT'
+return source</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -10171,7 +10180,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E42"/>
+  <dimension ref="A1:E43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
@@ -11376,6 +11385,37 @@
         </is>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-06-03 11:40:53</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>w10itasv</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>EDIT</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>TAXC</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Type: DIRECT-&gt;PYTHON, Val: ''-&gt;'if str(source).strip() == '001':
+    return 'TAX'
+elif str(source).strip() == '000':
+    return 'NOT'
+return source'</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
